--- a/examples/tabs/basic/tabs_config.xlsx
+++ b/examples/tabs/basic/tabs_config.xlsx
@@ -1,44 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Documents/Turas/templates/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46C28C7-48D6-A04F-AC36-D9EC426EE08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24500" yWindow="3360" windowWidth="25420" windowHeight="16140" xr2:uid="{AA660BF5-D3C1-BD42-AD32-4961F98E36EC}"/>
+    <workbookView xWindow="24500" yWindow="3360" windowWidth="25420" windowHeight="16140" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Settings" sheetId="1" r:id="rId1"/>
-    <sheet name="Selection" sheetId="2" r:id="rId2"/>
-    <sheet name="Base Filters" sheetId="3" r:id="rId3"/>
+    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Selection" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Base Filters" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <si>
     <t>Setting</t>
   </si>
@@ -648,33 +625,43 @@
   <si>
     <t>0-3</t>
   </si>
+  <si>
+    <t xml:space="preserve">Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate diagnostic stats pack workbook (Y/N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project name (appears in stats pack Declaration sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst name (appears in stats pack Declaration sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research_House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research organisation name (appears in stats pack Declaration sheet)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -685,20 +672,33 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <b/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+      <b/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="3">
@@ -727,16 +727,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,779 +1069,815 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90EE7A2F-61E0-874D-9844-95C6CF4AAE8E}">
-  <dimension ref="A1:D61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="39.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.83203125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+    <row r="7">
+      <c r="A7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="8">
+      <c r="A8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="4" t="b">
+      <c r="C9" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+    <row r="10">
+      <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+    <row r="11">
+      <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="4" t="b">
+      <c r="C11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+    <row r="12">
+      <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="4" t="b">
+      <c r="C12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+    <row r="13">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+    <row r="14">
+      <c r="A14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+    <row r="15">
+      <c r="A15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+    <row r="16">
+      <c r="A16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+    <row r="17">
+      <c r="A17" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="4" t="b">
+      <c r="C18" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+    <row r="19">
+      <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="4" t="b">
+      <c r="C19" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+    <row r="20">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="4" t="b">
+      <c r="C20" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+    <row r="21">
+      <c r="A21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+    <row r="22">
+      <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+    <row r="23">
+      <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+    <row r="24">
+      <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+    <row r="25">
+      <c r="A25" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="4" t="b">
+      <c r="C25" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+    <row r="26">
+      <c r="A26" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="4" t="b">
+      <c r="C27" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+    <row r="28">
+      <c r="A28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="4" t="b">
+      <c r="C28" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+    <row r="29">
+      <c r="A29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="4" t="b">
+      <c r="C29" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+    <row r="30">
+      <c r="A30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="4" t="b">
+      <c r="C31" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
+    <row r="32">
+      <c r="A32" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+    <row r="33">
+      <c r="A33" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+    <row r="34">
+      <c r="A34" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
+    <row r="35">
+      <c r="A35" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="4" t="b">
+      <c r="C35" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+    <row r="36">
+      <c r="A36" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
+    <row r="38">
+      <c r="A38" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
+    <row r="39">
+      <c r="A39" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
+    <row r="40">
+      <c r="A40" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+    <row r="41">
+      <c r="A41" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="4" t="b">
+      <c r="C42" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+    <row r="43">
+      <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
+      <c r="B43" s="1"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B44" s="4" t="b">
+      <c r="B44" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
+    <row r="45">
+      <c r="A45" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B45" s="4" t="b">
+      <c r="B45" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+    <row r="46">
+      <c r="A46" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B46" s="4" t="b">
+      <c r="B46" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
+    <row r="47">
+      <c r="A47" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B47" s="4" t="b">
+      <c r="B47" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
+    <row r="48">
+      <c r="A48" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B48" s="4" t="b">
+      <c r="B48" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+    <row r="49">
+      <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
+    <row r="50">
+      <c r="A50" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B50" s="4" t="b">
+      <c r="B50" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
+    <row r="51">
+      <c r="A51" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B51" s="4" t="b">
+      <c r="B51" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
+    <row r="52">
+      <c r="A52" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B52" s="4" t="b">
+      <c r="B52" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
+    <row r="53">
+      <c r="A53" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B53" s="4" t="b">
+      <c r="B53" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
+    <row r="54">
+      <c r="A54" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
+    <row r="55">
+      <c r="A55" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="8" t="s">
+    <row r="56">
+      <c r="A56" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
+    <row r="57">
+      <c r="A57" s="2" t="s">
         <v>170</v>
       </c>
       <c r="B57" t="s">
         <v>181</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
+    <row r="58">
+      <c r="A58" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B58" t="s">
         <v>181</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
+    <row r="59">
+      <c r="A59" s="2" t="s">
         <v>174</v>
       </c>
       <c r="B59" t="s">
         <v>181</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
+    <row r="60">
+      <c r="A60" s="2" t="s">
         <v>176</v>
       </c>
       <c r="B60" t="s">
         <v>181</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
+    <row r="61">
+      <c r="A61" s="2" t="s">
         <v>178</v>
       </c>
       <c r="B61" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="2" t="s">
         <v>179</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>188</v>
+      </c>
+      <c r="C64" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>190</v>
+      </c>
+      <c r="C65" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A345915-1627-8F40-8013-373418389E1C}">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="21" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="15" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1">
+      <c r="A1" s="6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2">
+      <c r="A2" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1873,222 +1908,223 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    <row r="5">
+      <c r="A5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6">
+      <c r="A6" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="2" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20EA9279-4195-274E-8956-905B687DACA1}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="22.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="22.1640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="40" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3">
+      <c r="A3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+    <row r="4">
+      <c r="A4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+    <row r="5">
+      <c r="A5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+    <row r="6">
+      <c r="A6" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8">
+      <c r="A8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>